--- a/Used_Sprites_Tracker.xlsx
+++ b/Used_Sprites_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pokemon TCG Legacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD31995B-8847-443A-80B5-54AE2978C9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0AB6E63-91D7-49C5-941B-E336B4EB83D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="43200" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprite Tracker" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="410">
   <si>
     <t>Name</t>
   </si>
@@ -52,12 +52,6 @@
     <t>1Pokemontrainer_RivalM</t>
   </si>
   <si>
-    <t>AceTrainer_F</t>
-  </si>
-  <si>
-    <t>AceTrainer_M</t>
-  </si>
-  <si>
     <t>Argenta</t>
   </si>
   <si>
@@ -1250,6 +1244,12 @@
   </si>
   <si>
     <t>Youngster3</t>
+  </si>
+  <si>
+    <t>Cooltrainer_F4</t>
+  </si>
+  <si>
+    <t>Cooltrainer_M4</t>
   </si>
 </sst>
 </file>
@@ -1669,28 +1669,33 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>409</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -1698,10 +1703,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
@@ -1709,58 +1714,63 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -1768,58 +1778,58 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" s="2"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B27" s="2"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B29" s="2"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C31" s="2">
         <v>4</v>
@@ -1827,16 +1837,16 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -1844,10 +1854,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -1855,195 +1865,200 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B35" s="2"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B36" s="2"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B44" s="2"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B45" s="2"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B48" s="2"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B49" s="2"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B50" s="2"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B52" s="2"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B54" s="2"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B55" s="2"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B56" s="2"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B57" s="2"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B58" s="2"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B59" s="2"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B60" s="2"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B61" s="2"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B62" s="2"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B63" s="2"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B64" s="2"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -2051,22 +2066,22 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B66" s="2"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B67" s="2"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -2074,148 +2089,153 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B69" s="2"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B70" s="2"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B71" s="2"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B72" s="2"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B73" s="2"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B74" s="2"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B75" s="2"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B76" s="2"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>79</v>
-      </c>
-      <c r="B77" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B78" s="2"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B79" s="2"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B80" s="2"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B81" s="2"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B82" s="2"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B83" s="2"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B84" s="2"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B85" s="2"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B86" s="2"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B87" s="2"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B88" s="2"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B89" s="2"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B90" s="2"/>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B91" s="2"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C92" s="2">
         <v>3</v>
@@ -2223,70 +2243,70 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B93" s="2"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B94" s="2"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B95" s="2"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B96" s="2"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B97" s="2"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B98" s="2"/>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B99" s="2"/>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B100" s="2"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B101" s="2"/>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B102" s="2"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C103" s="2">
         <v>2</v>
@@ -2294,16 +2314,16 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B104" s="2"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C105" s="2">
         <v>3</v>
@@ -2311,10 +2331,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C106" s="2">
         <v>2</v>
@@ -2322,10 +2342,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -2333,10 +2353,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C108" s="2">
         <v>7</v>
@@ -2344,10 +2364,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -2355,46 +2375,46 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B110" s="2"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B111" s="2"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B112" s="2"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B113" s="2"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B114" s="2"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B115" s="2"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -2402,10 +2422,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -2413,28 +2433,28 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B118" s="2"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B119" s="2"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B120" s="2"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -2442,16 +2462,16 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B122" s="2"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -2459,46 +2479,46 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B124" s="2"/>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B125" s="2"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B126" s="2"/>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B127" s="2"/>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B128" s="2"/>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B129" s="2"/>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -2506,40 +2526,40 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B131" s="2"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B132" s="2"/>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B133" s="2"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B134" s="2"/>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B135" s="2"/>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -2547,118 +2567,118 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B137" s="2"/>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B138" s="2"/>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B139" s="2"/>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B140" s="2"/>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B141" s="2"/>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B142" s="2"/>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B143" s="2"/>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B144" s="2"/>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B145" s="2"/>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B146" s="2"/>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B147" s="2"/>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B148" s="2"/>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B149" s="2"/>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B150" s="2"/>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B151" s="2"/>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B152" s="2"/>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B153" s="2"/>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B154" s="2"/>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C155" s="2">
         <v>1</v>
@@ -2666,10 +2686,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C156" s="2">
         <v>1</v>
@@ -2677,28 +2697,28 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B157" s="2"/>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B158" s="2"/>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B159" s="2"/>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C160" s="2">
         <v>1</v>
@@ -2706,28 +2726,28 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B161" s="2"/>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B162" s="2"/>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B163" s="2"/>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C164" s="2">
         <v>2</v>
@@ -2735,52 +2755,57 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>167</v>
-      </c>
-      <c r="B165" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C165" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B166" s="2"/>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B167" s="2"/>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B168" s="2"/>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B169" s="2"/>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B170" s="2"/>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B171" s="2"/>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C172" s="2">
         <v>1</v>
@@ -2788,22 +2813,22 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B173" s="2"/>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B174" s="2"/>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C175" s="2">
         <v>1</v>
@@ -2811,16 +2836,21 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>178</v>
-      </c>
-      <c r="B176" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C176" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C177" s="2">
         <v>1</v>
@@ -2828,16 +2858,16 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B178" s="2"/>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C179" s="2">
         <v>2</v>
@@ -2845,82 +2875,82 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B180" s="2"/>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B181" s="2"/>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B182" s="2"/>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B183" s="2"/>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B184" s="2"/>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B185" s="2"/>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B186" s="2"/>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B187" s="2"/>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B188" s="2"/>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B189" s="2"/>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B190" s="2"/>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B191" s="2"/>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C192" s="2">
         <v>1</v>
@@ -2928,10 +2958,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C193" s="2">
         <v>1</v>
@@ -2939,10 +2969,10 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C194" s="2">
         <v>3</v>
@@ -2950,10 +2980,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C195" s="2">
         <v>2</v>
@@ -2961,10 +2991,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C196" s="2">
         <v>1</v>
@@ -2972,10 +3002,10 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C197" s="2">
         <v>1</v>
@@ -2983,10 +3013,10 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C198" s="2">
         <v>1</v>
@@ -2994,10 +3024,10 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C199" s="2">
         <v>1</v>
@@ -3005,10 +3035,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C200" s="2">
         <v>1</v>
@@ -3016,10 +3046,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C201" s="2">
         <v>1</v>
@@ -3027,10 +3057,10 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C202" s="2">
         <v>2</v>
@@ -3038,10 +3068,10 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C203" s="2">
         <v>1</v>
@@ -3049,10 +3079,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C204" s="2">
         <v>2</v>
@@ -3060,10 +3090,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C205" s="2">
         <v>1</v>
@@ -3071,10 +3101,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C206" s="2">
         <v>3</v>
@@ -3082,16 +3112,16 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B207" s="2"/>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C208" s="2">
         <v>1</v>
@@ -3099,16 +3129,16 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B209" s="2"/>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C210" s="2">
         <v>1</v>
@@ -3116,10 +3146,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C211" s="2">
         <v>1</v>
@@ -3127,28 +3157,28 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B212" s="2"/>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B213" s="2"/>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B214" s="2"/>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C215" s="2">
         <v>1</v>
@@ -3156,22 +3186,22 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B216" s="2"/>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B217" s="2"/>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C218" s="2">
         <v>3</v>
@@ -3179,10 +3209,10 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C219" s="2">
         <v>2</v>
@@ -3190,16 +3220,16 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B220" s="2"/>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C221" s="2">
         <v>4</v>
@@ -3207,28 +3237,28 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B222" s="2"/>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B223" s="2"/>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B224" s="2"/>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C225" s="2">
         <v>1</v>
@@ -3236,10 +3266,10 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C226" s="2">
         <v>4</v>
@@ -3247,10 +3277,10 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C227" s="2">
         <v>1</v>
@@ -3258,310 +3288,310 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B228" s="2"/>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B229" s="2"/>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B230" s="2"/>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B231" s="2"/>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B232" s="2"/>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B233" s="2"/>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B234" s="2"/>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B235" s="2"/>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B236" s="2"/>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B237" s="2"/>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B238" s="2"/>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B239" s="2"/>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B240" s="2"/>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B241" s="2"/>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B242" s="2"/>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B243" s="2"/>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B244" s="2"/>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B245" s="2"/>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B246" s="2"/>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B247" s="2"/>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B248" s="2"/>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B249" s="2"/>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B250" s="2"/>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B251" s="2"/>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B252" s="2"/>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B253" s="2"/>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B254" s="2"/>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B255" s="2"/>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B256" s="2"/>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B257" s="2"/>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B258" s="2"/>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B259" s="2"/>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B260" s="2"/>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B261" s="2"/>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B262" s="2"/>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B263" s="2"/>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B264" s="2"/>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B265" s="2"/>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B266" s="2"/>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B267" s="2"/>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B268" s="2"/>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B269" s="2"/>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B270" s="2"/>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B271" s="2"/>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B272" s="2"/>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B273" s="2"/>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B274" s="2"/>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B275" s="2"/>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B276" s="2"/>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B277" s="2"/>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C278" s="2">
         <v>1</v>
@@ -3569,10 +3599,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C279" s="2">
         <v>1</v>
@@ -3580,10 +3610,10 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C280" s="2">
         <v>1</v>
@@ -3591,10 +3621,10 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C281" s="2">
         <v>1</v>
@@ -3602,10 +3632,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C282" s="2">
         <v>1</v>
@@ -3613,58 +3643,58 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B283" s="2"/>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B284" s="2"/>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B285" s="2"/>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B286" s="2"/>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B287" s="2"/>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B288" s="2"/>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B289" s="2"/>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B290" s="2"/>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C291" s="2">
         <v>1</v>
@@ -3672,28 +3702,28 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B292" s="2"/>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B293" s="2"/>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B294" s="2"/>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C295" s="2">
         <v>6</v>
@@ -3701,40 +3731,40 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B296" s="2"/>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B297" s="2"/>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B298" s="2"/>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B299" s="2"/>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B300" s="2"/>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C301" s="2">
         <v>1</v>
@@ -3742,46 +3772,46 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B302" s="2"/>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B303" s="2"/>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B304" s="2"/>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B305" s="2"/>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B306" s="2"/>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B307" s="2"/>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C308" s="2">
         <v>1</v>
@@ -3789,52 +3819,52 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B309" s="2"/>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B310" s="2"/>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B311" s="2"/>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B312" s="2"/>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B313" s="2"/>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B314" s="2"/>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B315" s="2"/>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C316" s="2">
         <v>1</v>
@@ -3842,40 +3872,40 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B317" s="2"/>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B318" s="2"/>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B319" s="2"/>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B320" s="2"/>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B321" s="2"/>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C322" s="2">
         <v>1</v>
@@ -3883,10 +3913,10 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C323" s="2">
         <v>2</v>
@@ -3894,16 +3924,21 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>326</v>
-      </c>
-      <c r="B324" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C324" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C325" s="2">
         <v>1</v>
@@ -3911,16 +3946,16 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B326" s="2"/>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C327" s="2">
         <v>4</v>
@@ -3928,64 +3963,64 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B328" s="2"/>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B329" s="2"/>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B330" s="2"/>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B331" s="2"/>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B332" s="2"/>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B333" s="2"/>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B334" s="2"/>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B335" s="2"/>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B336" s="2"/>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C337" s="2">
         <v>1</v>
@@ -3993,10 +4028,10 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C338" s="2">
         <v>1</v>
@@ -4004,88 +4039,88 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B339" s="2"/>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B340" s="2"/>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B341" s="2"/>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B342" s="2"/>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B343" s="2"/>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B344" s="2"/>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B345" s="2"/>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B346" s="2"/>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B347" s="2"/>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B348" s="2"/>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B349" s="2"/>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B350" s="2"/>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B351" s="2"/>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C352" s="2">
         <v>1</v>
@@ -4093,10 +4128,10 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C353" s="2">
         <v>1</v>
@@ -4104,10 +4139,10 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C354" s="2">
         <v>1</v>
@@ -4115,10 +4150,10 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C355" s="2">
         <v>1</v>
@@ -4126,136 +4161,136 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B356" s="2"/>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B357" s="2"/>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B358" s="2"/>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B359" s="2"/>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B360" s="2"/>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B361" s="2"/>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B362" s="2"/>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B363" s="2"/>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B364" s="2"/>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B365" s="2"/>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B366" s="2"/>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B367" s="2"/>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B368" s="2"/>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B369" s="2"/>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B370" s="2"/>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B371" s="2"/>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B372" s="2"/>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B373" s="2"/>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B374" s="2"/>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B375" s="2"/>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B376" s="2"/>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C377" s="2">
         <v>1</v>
@@ -4263,10 +4298,10 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C378" s="2">
         <v>2</v>
@@ -4274,10 +4309,10 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C379" s="2">
         <v>1</v>
@@ -4285,16 +4320,16 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B380" s="2"/>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C381" s="2">
         <v>1</v>
@@ -4302,10 +4337,10 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C382" s="2">
         <v>1</v>
@@ -4313,10 +4348,10 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C383" s="2">
         <v>1</v>
@@ -4324,10 +4359,10 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C384" s="2">
         <v>1</v>
@@ -4335,10 +4370,10 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C385" s="2">
         <v>1</v>
@@ -4346,10 +4381,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C386" s="2">
         <v>1</v>
@@ -4357,10 +4392,10 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C387" s="2">
         <v>1</v>
@@ -4368,46 +4403,46 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B388" s="2"/>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B389" s="2"/>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B390" s="2"/>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B391" s="2"/>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B392" s="2"/>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B393" s="2"/>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C394" s="2">
         <v>1</v>
@@ -4415,16 +4450,16 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B395" s="2"/>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C396" s="2">
         <v>1</v>
@@ -4432,16 +4467,16 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B397" s="2"/>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C398" s="2">
         <v>2</v>
@@ -4449,22 +4484,22 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B399" s="2"/>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B400" s="2"/>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C401" s="2">
         <v>1</v>
@@ -4472,10 +4507,10 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C402" s="2">
         <v>1</v>
@@ -4483,10 +4518,10 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C403" s="2">
         <v>1</v>
@@ -4494,10 +4529,10 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C404" s="2">
         <v>1</v>
@@ -4505,16 +4540,16 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B405" s="2"/>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C406" s="2">
         <v>1</v>
@@ -4522,10 +4557,10 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C407" s="2">
         <v>1</v>

--- a/Used_Sprites_Tracker.xlsx
+++ b/Used_Sprites_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pokemon TCG Legacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0AB6E63-91D7-49C5-941B-E336B4EB83D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0CACDA-02BE-4BE5-9727-FF489B7E6A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="43200" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprite Tracker" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="409">
   <si>
     <t>Name</t>
   </si>
@@ -581,9 +581,6 @@
   </si>
   <si>
     <t>Medium</t>
-  </si>
-  <si>
-    <t>Medium_1</t>
   </si>
   <si>
     <t>Mira</t>
@@ -1269,6 +1266,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1606,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C407"/>
+  <dimension ref="A1:C406"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1669,7 +1667,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -1680,7 +1678,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B10" s="2"/>
     </row>
@@ -2913,7 +2911,12 @@
       <c r="A186" t="s">
         <v>186</v>
       </c>
-      <c r="B186" s="2"/>
+      <c r="B186" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C186" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
@@ -2943,7 +2946,12 @@
       <c r="A191" t="s">
         <v>191</v>
       </c>
-      <c r="B191" s="2"/>
+      <c r="B191" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C191" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
@@ -2964,7 +2972,7 @@
         <v>12</v>
       </c>
       <c r="C193" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -2975,7 +2983,7 @@
         <v>12</v>
       </c>
       <c r="C194" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -2986,7 +2994,7 @@
         <v>12</v>
       </c>
       <c r="C195" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -3052,7 +3060,7 @@
         <v>12</v>
       </c>
       <c r="C201" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -3063,7 +3071,7 @@
         <v>12</v>
       </c>
       <c r="C202" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -3074,7 +3082,7 @@
         <v>12</v>
       </c>
       <c r="C203" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -3085,7 +3093,7 @@
         <v>12</v>
       </c>
       <c r="C204" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -3096,42 +3104,42 @@
         <v>12</v>
       </c>
       <c r="C205" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>206</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C206" s="2">
-        <v>3</v>
-      </c>
+      <c r="B206" s="2"/>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>207</v>
       </c>
-      <c r="B207" s="2"/>
+      <c r="B207" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C207" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>208</v>
       </c>
-      <c r="B208" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C208" s="2">
-        <v>1</v>
-      </c>
+      <c r="B208" s="2"/>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>209</v>
       </c>
-      <c r="B209" s="2"/>
+      <c r="B209" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C209" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
@@ -3148,12 +3156,7 @@
       <c r="A211" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C211" s="2">
-        <v>1</v>
-      </c>
+      <c r="B211" s="2"/>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
@@ -3171,18 +3174,18 @@
       <c r="A214" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="2"/>
+      <c r="B214" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C214" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C215" s="2">
-        <v>1</v>
-      </c>
+      <c r="B215" s="2"/>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
@@ -3194,7 +3197,12 @@
       <c r="A217" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="2"/>
+      <c r="B217" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C217" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
@@ -3204,36 +3212,31 @@
         <v>12</v>
       </c>
       <c r="C218" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>219</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C219" s="2">
-        <v>2</v>
-      </c>
+      <c r="B219" s="2"/>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>220</v>
       </c>
-      <c r="B220" s="2"/>
+      <c r="B220" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C220" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>221</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C221" s="2">
-        <v>4</v>
-      </c>
+      <c r="B221" s="2"/>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
@@ -3251,7 +3254,12 @@
       <c r="A224" t="s">
         <v>224</v>
       </c>
-      <c r="B224" s="2"/>
+      <c r="B224" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C224" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
@@ -3261,7 +3269,7 @@
         <v>12</v>
       </c>
       <c r="C225" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -3272,19 +3280,14 @@
         <v>12</v>
       </c>
       <c r="C226" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>227</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C227" s="2">
-        <v>1</v>
-      </c>
+      <c r="B227" s="2"/>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
@@ -3584,7 +3587,12 @@
       <c r="A277" t="s">
         <v>277</v>
       </c>
-      <c r="B277" s="2"/>
+      <c r="B277" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C277" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
@@ -3634,12 +3642,7 @@
       <c r="A282" t="s">
         <v>282</v>
       </c>
-      <c r="B282" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C282" s="2">
-        <v>1</v>
-      </c>
+      <c r="B282" s="2"/>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
@@ -3687,18 +3690,18 @@
       <c r="A290" t="s">
         <v>290</v>
       </c>
-      <c r="B290" s="2"/>
+      <c r="B290" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C290" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>291</v>
       </c>
-      <c r="B291" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C291" s="2">
-        <v>1</v>
-      </c>
+      <c r="B291" s="2"/>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
@@ -3716,18 +3719,18 @@
       <c r="A294" t="s">
         <v>294</v>
       </c>
-      <c r="B294" s="2"/>
+      <c r="B294" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C294" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>295</v>
       </c>
-      <c r="B295" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C295" s="2">
-        <v>6</v>
-      </c>
+      <c r="B295" s="2"/>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
@@ -3757,7 +3760,12 @@
       <c r="A300" t="s">
         <v>300</v>
       </c>
-      <c r="B300" s="2"/>
+      <c r="B300" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C300" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
@@ -3804,7 +3812,12 @@
       <c r="A307" t="s">
         <v>307</v>
       </c>
-      <c r="B307" s="2"/>
+      <c r="B307" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C307" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
@@ -3857,18 +3870,18 @@
       <c r="A315" t="s">
         <v>315</v>
       </c>
-      <c r="B315" s="2"/>
+      <c r="B315" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C315" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>316</v>
       </c>
-      <c r="B316" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C316" s="2">
-        <v>1</v>
-      </c>
+      <c r="B316" s="2"/>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
@@ -3898,7 +3911,12 @@
       <c r="A321" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="2"/>
+      <c r="B321" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C321" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
@@ -3908,7 +3926,7 @@
         <v>12</v>
       </c>
       <c r="C322" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -3919,7 +3937,7 @@
         <v>12</v>
       </c>
       <c r="C323" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -3948,18 +3966,18 @@
       <c r="A326" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="2"/>
+      <c r="B326" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C326" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C327" s="2">
-        <v>4</v>
-      </c>
+      <c r="B327" s="2"/>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
@@ -4013,7 +4031,12 @@
       <c r="A336" t="s">
         <v>336</v>
       </c>
-      <c r="B336" s="2"/>
+      <c r="B336" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C336" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
@@ -4030,12 +4053,7 @@
       <c r="A338" t="s">
         <v>338</v>
       </c>
-      <c r="B338" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C338" s="2">
-        <v>1</v>
-      </c>
+      <c r="B338" s="2"/>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
@@ -4113,7 +4131,12 @@
       <c r="A351" t="s">
         <v>351</v>
       </c>
-      <c r="B351" s="2"/>
+      <c r="B351" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C351" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
@@ -4152,12 +4175,7 @@
       <c r="A355" t="s">
         <v>355</v>
       </c>
-      <c r="B355" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C355" s="2">
-        <v>1</v>
-      </c>
+      <c r="B355" s="2"/>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
@@ -4283,7 +4301,12 @@
       <c r="A376" t="s">
         <v>376</v>
       </c>
-      <c r="B376" s="2"/>
+      <c r="B376" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C376" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
@@ -4293,7 +4316,7 @@
         <v>12</v>
       </c>
       <c r="C377" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -4304,25 +4327,25 @@
         <v>12</v>
       </c>
       <c r="C378" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>379</v>
       </c>
-      <c r="B379" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C379" s="2">
-        <v>1</v>
-      </c>
+      <c r="B379" s="2"/>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>380</v>
       </c>
-      <c r="B380" s="2"/>
+      <c r="B380" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C380" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
@@ -4394,12 +4417,7 @@
       <c r="A387" t="s">
         <v>387</v>
       </c>
-      <c r="B387" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C387" s="2">
-        <v>1</v>
-      </c>
+      <c r="B387" s="2"/>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
@@ -4435,52 +4453,52 @@
       <c r="A393" t="s">
         <v>393</v>
       </c>
-      <c r="B393" s="2"/>
+      <c r="B393" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C393" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>394</v>
       </c>
-      <c r="B394" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C394" s="2">
-        <v>1</v>
-      </c>
+      <c r="B394" s="2"/>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>395</v>
       </c>
-      <c r="B395" s="2"/>
+      <c r="B395" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C395" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>396</v>
       </c>
-      <c r="B396" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C396" s="2">
-        <v>1</v>
-      </c>
+      <c r="B396" s="2"/>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>397</v>
       </c>
-      <c r="B397" s="2"/>
+      <c r="B397" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C397" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>398</v>
       </c>
-      <c r="B398" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C398" s="2">
-        <v>2</v>
-      </c>
+      <c r="B398" s="2"/>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
@@ -4492,7 +4510,12 @@
       <c r="A400" t="s">
         <v>400</v>
       </c>
-      <c r="B400" s="2"/>
+      <c r="B400" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C400" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
@@ -4542,7 +4565,12 @@
       <c r="A405" t="s">
         <v>405</v>
       </c>
-      <c r="B405" s="2"/>
+      <c r="B405" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C405" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
@@ -4552,17 +4580,6 @@
         <v>12</v>
       </c>
       <c r="C406" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A407" t="s">
-        <v>407</v>
-      </c>
-      <c r="B407" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C407" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Used_Sprites_Tracker.xlsx
+++ b/Used_Sprites_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pokemon TCG Legacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0CACDA-02BE-4BE5-9727-FF489B7E6A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E191171D-7C0E-4701-8037-AF4927B28FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28785" yWindow="0" windowWidth="28920" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprite Tracker" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="409">
   <si>
     <t>Name</t>
   </si>
@@ -3834,13 +3834,17 @@
       <c r="A309" t="s">
         <v>309</v>
       </c>
-      <c r="B309" s="2"/>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>310</v>
       </c>
-      <c r="B310" s="2"/>
+      <c r="B310" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C310" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
